--- a/upload/mapadosite.xlsx
+++ b/upload/mapadosite.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="237">
   <si>
     <t>Categoria</t>
   </si>
@@ -89,15 +89,9 @@
     <t>https://www.transparencia.mg.gov.br/licitacoes</t>
   </si>
   <si>
-    <t>Convênios</t>
-  </si>
-  <si>
     <t>https://www.transparencia.mg.gov.br/transferencias-municipios</t>
   </si>
   <si>
-    <t>Obras</t>
-  </si>
-  <si>
     <t>https://www.transparencia.mg.gov.br/obras</t>
   </si>
   <si>
@@ -128,15 +122,9 @@
     <t>https://www.transparencia.mg.gov.br/pagina/estrutura-do-governo</t>
   </si>
   <si>
-    <t>Consultas</t>
-  </si>
-  <si>
     <t>Planejamento e Resultados</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/planejamento-e-resultados</t>
-  </si>
-  <si>
     <t>Leis Orçamentárias</t>
   </si>
   <si>
@@ -257,9 +245,6 @@
     <t>https://www.transparencia.mg.gov.br/processos-seletivos</t>
   </si>
   <si>
-    <t>Gestão Fiscal</t>
-  </si>
-  <si>
     <t>Relatório de Gestão Fiscal – RGF</t>
   </si>
   <si>
@@ -365,9 +350,6 @@
     <t>https://www.transparencia.mg.gov.br/cafimp</t>
   </si>
   <si>
-    <t>Transferências</t>
-  </si>
-  <si>
     <t>Transferências de impostos a municípios</t>
   </si>
   <si>
@@ -377,18 +359,6 @@
     <t>https://www.transparencia.mg.gov.br/transferencias-federais</t>
   </si>
   <si>
-    <t>Convênios de saída</t>
-  </si>
-  <si>
-    <t>https://www.transparencia.mg.gov.br/convenios-saida</t>
-  </si>
-  <si>
-    <t>Convênios de entrada</t>
-  </si>
-  <si>
-    <t>https://www.transparencia.mg.gov.br/convenios-entrada</t>
-  </si>
-  <si>
     <t>Termos de Parcerias</t>
   </si>
   <si>
@@ -446,9 +416,6 @@
     <t>Julgamento das Contas pelo TCE</t>
   </si>
   <si>
-    <t>Transparência Temática</t>
-  </si>
-  <si>
     <t>Acordo Judicial de Reparação da Vale</t>
   </si>
   <si>
@@ -467,9 +434,6 @@
     <t>https://www.transparencia.mg.gov.br/covid19</t>
   </si>
   <si>
-    <t>Desenvolvimento Social</t>
-  </si>
-  <si>
     <t>Auxílios Financeiros</t>
   </si>
   <si>
@@ -482,9 +446,6 @@
     <t>https://www.transparencia.mg.gov.br/transferencia-renda</t>
   </si>
   <si>
-    <t>Dívidas</t>
-  </si>
-  <si>
     <t>Dívida Ativa</t>
   </si>
   <si>
@@ -494,9 +455,6 @@
     <t>Gestão da Dívida Pública</t>
   </si>
   <si>
-    <t>Educação</t>
-  </si>
-  <si>
     <t>Plano Estadual de Educação</t>
   </si>
   <si>
@@ -527,9 +485,6 @@
     <t>https://www.transparencia.mg.gov.br/vagas-temporarias</t>
   </si>
   <si>
-    <t>Empresas</t>
-  </si>
-  <si>
     <t>Registro Público de Empresas</t>
   </si>
   <si>
@@ -542,9 +497,6 @@
     <t>https://www.transparencia.mg.gov.br/empresas-sancionadas</t>
   </si>
   <si>
-    <t>Meio Ambiente</t>
-  </si>
-  <si>
     <t>Portal do Meio Ambiente</t>
   </si>
   <si>
@@ -578,18 +530,12 @@
     <t>https://www.transparencia.mg.gov.br/compras-obras</t>
   </si>
   <si>
-    <t>Patrimônio Cultural</t>
-  </si>
-  <si>
     <t>Patrimônio Artístico e Cultural</t>
   </si>
   <si>
     <t>https://www.transparencia.mg.gov.br/patrimonio-cultural</t>
   </si>
   <si>
-    <t>Saúde</t>
-  </si>
-  <si>
     <t>Plano Estadual de Saúde 2024-2027</t>
   </si>
   <si>
@@ -644,9 +590,6 @@
     <t>https://www.transparencia.mg.gov.br/dados-saude</t>
   </si>
   <si>
-    <t>Segurança</t>
-  </si>
-  <si>
     <t>Crimes Violentos</t>
   </si>
   <si>
@@ -690,6 +633,108 @@
   </si>
   <si>
     <t>Ouvidoria Geral do Estado</t>
+  </si>
+  <si>
+    <t>Propostas e Alterações Orçamentárias</t>
+  </si>
+  <si>
+    <t>Portal da Transparência</t>
+  </si>
+  <si>
+    <t>Planejamento e Monitoramento do PPAG</t>
+  </si>
+  <si>
+    <t>Despesas Públicas</t>
+  </si>
+  <si>
+    <t>Relatórios da Lei de Responsabilidade Fiscal – LRF</t>
+  </si>
+  <si>
+    <t>Licitações e Contratos</t>
+  </si>
+  <si>
+    <t>Transferências Obrigatórias</t>
+  </si>
+  <si>
+    <t>Convênios de Saída</t>
+  </si>
+  <si>
+    <t>Convênios de Entrada</t>
+  </si>
+  <si>
+    <t>Convênios / Parcerias de Saída de Recursos</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/convenios/convenios-de-saida-de-recursos/convenios-de-saida</t>
+  </si>
+  <si>
+    <t>Convênios de Saída e Parceria MROSC  </t>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/view?r=eyJrIjoiMzY1NjVkNzgtZDlhYy00ZWI0LThhM2UtMjY5MzliMzkzYWU2IiwidCI6ImU1ZDNhZTdjLTliMzgtNDhkZS1hMDg3LWY2NzM0YTI4NzU3NCJ9</t>
+  </si>
+  <si>
+    <t>Convênios e Parcerias</t>
+  </si>
+  <si>
+    <t>Convênios de Entrada de Recursos</t>
+  </si>
+  <si>
+    <t>Convênios de Entrada – Portal Federal</t>
+  </si>
+  <si>
+    <t>Painel de Monitoramenteo dos Instrumentos de Entrada de Recursos</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/convenios/convenios-de-entrada/convenio-entrada</t>
+  </si>
+  <si>
+    <t>https://portaldatransparencia.gov.br/convenios/consulta?paginacaoSimples=true&amp;tamanhoPagina=&amp;offset=&amp;direcaoOrdenacao=asc&amp;periodoLiberacaoRecursosDe=01%2F01%2F2020&amp;periodoVigenciaDe=01%2F01%2F2020&amp;periodoVigenciaAte=30%2F09%2F2023&amp;tipoConvenente=8&amp;uf=MG&amp;colunasSelecionadas=linkDetalhamento%2CnumeroConvenio%2Cuf%2CmunicipioConvenente%2Csituacao%2CtipoTransferencia%2Cobjetivo%2CorgaoSuperior%2Corgao%2Cconcedente%2Cconvenente%2CdataInicioVigencia%2CdataFimVigencia%2CdataPublicacao%2CvalorLiberado%2</t>
+  </si>
+  <si>
+    <t>https://www.casacivil.mg.gov.br/CaptacaoRecursos/Detalhe/44</t>
+  </si>
+  <si>
+    <t>Transparência Temática - Acordos</t>
+  </si>
+  <si>
+    <t>Transparência Temática - COVID</t>
+  </si>
+  <si>
+    <t>Transparência Temática - Desenvolvimento Social</t>
+  </si>
+  <si>
+    <t>Transparência Temática - Dívidas</t>
+  </si>
+  <si>
+    <t>https://dataviva.info/</t>
+  </si>
+  <si>
+    <t>Economia</t>
+  </si>
+  <si>
+    <t>Transparência Temática - Economia</t>
+  </si>
+  <si>
+    <t>Transparência Temática - Educação</t>
+  </si>
+  <si>
+    <t>Transparência Temática - Empresas</t>
+  </si>
+  <si>
+    <t>Transparência Temática - Meio Ambiente</t>
+  </si>
+  <si>
+    <t>Transparência Temática - Obras</t>
+  </si>
+  <si>
+    <t>Transparência Temática - Patrimônio Artístico e Cultural</t>
+  </si>
+  <si>
+    <t>Transparência Temática - Saúde</t>
+  </si>
+  <si>
+    <t>Transparência Temática - Segurança</t>
   </si>
 </sst>
 </file>
@@ -742,7 +787,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -753,6 +798,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1034,11 +1080,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C99"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="95.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1069,10 +1115,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1102,114 +1148,114 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>203</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>205</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>205</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1220,18 +1266,18 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>206</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>14</v>
@@ -1242,24 +1288,24 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>206</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>206</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1267,7 +1313,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>17</v>
@@ -1278,10 +1324,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1289,10 +1335,10 @@
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1300,10 +1346,10 @@
         <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1311,10 +1357,10 @@
         <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1322,161 +1368,161 @@
         <v>16</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="C32" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="C39" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>18</v>
@@ -1484,40 +1530,40 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>19</v>
@@ -1528,614 +1574,658 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>119</v>
+        <v>214</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>120</v>
+        <v>215</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>121</v>
+        <v>217</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>122</v>
+        <v>220</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>123</v>
+        <v>218</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>125</v>
+        <v>219</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>25</v>
+        <v>216</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>147</v>
+        <v>223</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>147</v>
+        <v>223</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>152</v>
+        <v>224</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>152</v>
+        <v>225</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>26</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>156</v>
+        <v>229</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>163</v>
+        <v>228</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>164</v>
+        <v>227</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>23</v>
+        <v>231</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>23</v>
+        <v>232</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>23</v>
+        <v>232</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>184</v>
+        <v>232</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>191</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>29</v>
+        <v>185</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>220</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C103" s="2" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1"/>
-    <hyperlink ref="C7" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/upload/mapadosite.xlsx
+++ b/upload/mapadosite.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678A4233-E537-4BC7-A922-0C625B194E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="234">
   <si>
     <t>Categoria</t>
   </si>
@@ -47,9 +48,6 @@
     <t>Glossário</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/pagina/glossario</t>
-  </si>
-  <si>
     <t>Legislação</t>
   </si>
   <si>
@@ -65,63 +63,27 @@
     <t>Receitas</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/receita</t>
-  </si>
-  <si>
     <t>Despesas</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/despesa</t>
-  </si>
-  <si>
     <t>Pessoal</t>
   </si>
   <si>
     <t>https://www.transparencia.mg.gov.br/remuneracao</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/diarias</t>
-  </si>
-  <si>
     <t>Licitações</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/licitacoes</t>
-  </si>
-  <si>
-    <t>https://www.transparencia.mg.gov.br/transferencias-municipios</t>
-  </si>
-  <si>
-    <t>https://www.transparencia.mg.gov.br/obras</t>
-  </si>
-  <si>
     <t>Patrimônio</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/divida-publica</t>
-  </si>
-  <si>
-    <t>https://www.transparencia.mg.gov.br/contas-governador</t>
-  </si>
-  <si>
-    <t>https://www.transparencia.mg.gov.br/ouvidoria</t>
-  </si>
-  <si>
-    <t>https://www.transparencia.mg.gov.br/e-sic</t>
-  </si>
-  <si>
     <t>Histórico de Atualizações</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/pagina/historico-de-atualizacoes</t>
-  </si>
-  <si>
     <t>Estrutura do Governo</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/pagina/estrutura-do-governo</t>
-  </si>
-  <si>
     <t>Planejamento e Resultados</t>
   </si>
   <si>
@@ -134,78 +96,42 @@
     <t>Proposta Orçamentária</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/proposta-orcamentaria</t>
-  </si>
-  <si>
     <t>Emendas ao Projeto da LOA</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/emendas-loa</t>
-  </si>
-  <si>
     <t>Alteração Orçamentária</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/alteracao-orcamentaria</t>
-  </si>
-  <si>
     <t>Crédito Orçamentário</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/credito-orcamentario</t>
-  </si>
-  <si>
     <t>Obras Orçadas</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/obras-orcadas</t>
-  </si>
-  <si>
     <t>Programação e Execução do PPAG por Programa</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/ppag-programa</t>
-  </si>
-  <si>
     <t>Programação e Execução – Consolidado</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/ppag-consolidado</t>
-  </si>
-  <si>
     <t>Renúncias e Desonerações</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/renuncias</t>
-  </si>
-  <si>
     <t>Restos a Pagar</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/restos-a-pagar</t>
-  </si>
-  <si>
     <t>Mapa de Investimento</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/mapa-investimentos</t>
-  </si>
-  <si>
     <t>Remuneração dos Servidores</t>
   </si>
   <si>
     <t>Despesa com Pessoal</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/despesa-pessoal</t>
-  </si>
-  <si>
     <t>Estagiários</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/estagiarios</t>
-  </si>
-  <si>
     <t>Terceirizados</t>
   </si>
   <si>
@@ -215,99 +141,54 @@
     <t>Relação Nominal dos Servidores</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/servidores</t>
-  </si>
-  <si>
     <t>Cadastro CEAPE</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/ceape</t>
-  </si>
-  <si>
     <t>Concursos</t>
   </si>
   <si>
     <t>Concursos realizados</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/concursos</t>
-  </si>
-  <si>
     <t>Editais concursos públicos</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/editais-concursos</t>
-  </si>
-  <si>
     <t>Processos seletivos</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/processos-seletivos</t>
-  </si>
-  <si>
     <t>Relatório de Gestão Fiscal – RGF</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/rgf</t>
-  </si>
-  <si>
     <t>Relatório Resumido da Execução Orçamentária – RREO</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/rreo</t>
-  </si>
-  <si>
     <t>Demonstrativos Quadrimestrais</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/demonstrativos</t>
-  </si>
-  <si>
     <t>Índices Constitucionais</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/indices-constitucionais</t>
-  </si>
-  <si>
     <t>Programas de Reestruturação e Ajuste</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/programas-ajuste</t>
-  </si>
-  <si>
     <t>Fundo de Erradicação da Miséria</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/fundo-miseria</t>
-  </si>
-  <si>
     <t>Programas Sociais</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/programas-sociais</t>
-  </si>
-  <si>
     <t>Incentivos</t>
   </si>
   <si>
     <t>Incentivos Culturais</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/incentivos-culturais</t>
-  </si>
-  <si>
     <t>Incentivos Esportivos</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/incentivos-esportivos</t>
-  </si>
-  <si>
     <t>Crédito e Financiamento do Setor Público</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/credito-setor-publico</t>
-  </si>
-  <si>
     <t>Viagens</t>
   </si>
   <si>
@@ -317,291 +198,153 @@
     <t>Voos do Governador</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/voos-governador</t>
-  </si>
-  <si>
     <t>Compras e contratos</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/compras</t>
-  </si>
-  <si>
     <t>Notas Fiscais</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/notas-fiscais</t>
-  </si>
-  <si>
     <t>Plano anual de compras – PAC</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/pac</t>
-  </si>
-  <si>
     <t>Fiscais de contrato</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/fiscais-contrato</t>
-  </si>
-  <si>
     <t>CAFIMP</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/cafimp</t>
-  </si>
-  <si>
     <t>Transferências de impostos a municípios</t>
   </si>
   <si>
     <t>Transferências recebidas do Governo Federal</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/transferencias-federais</t>
-  </si>
-  <si>
     <t>Termos de Parcerias</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/termos-parceria</t>
-  </si>
-  <si>
     <t>Acordos de Cooperação Técnica</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/acordos-cooperacao</t>
-  </si>
-  <si>
     <t>Parcerias Público Privadas</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/ppp</t>
-  </si>
-  <si>
     <t>Emendas Parlamentares</t>
   </si>
   <si>
     <t>Painel de Emendas Estaduais</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/emendas-estaduais</t>
-  </si>
-  <si>
-    <t>Execução das Emendas Parlamentares</t>
-  </si>
-  <si>
-    <t>https://www.transparencia.mg.gov.br/execucao-emendas</t>
-  </si>
-  <si>
     <t>Frota</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/frota</t>
-  </si>
-  <si>
     <t>Bens Móveis</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/bens-moveis</t>
-  </si>
-  <si>
     <t>Contas do Governador</t>
   </si>
   <si>
     <t>Relatório de Gestão e Balanço Geral do Estado</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/balanco-geral</t>
-  </si>
-  <si>
     <t>Julgamento das Contas pelo TCE</t>
   </si>
   <si>
     <t>Acordo Judicial de Reparação da Vale</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/acordo-vale</t>
-  </si>
-  <si>
     <t>Despesa de Pessoal – Acordo Vale</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/despesa-vale</t>
-  </si>
-  <si>
     <t>COVID-19</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/covid19</t>
-  </si>
-  <si>
     <t>Auxílios Financeiros</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/auxilios</t>
-  </si>
-  <si>
     <t>Programas de Transferência de Renda</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/transferencia-renda</t>
-  </si>
-  <si>
     <t>Dívida Ativa</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/divida-ativa</t>
-  </si>
-  <si>
     <t>Gestão da Dívida Pública</t>
   </si>
   <si>
     <t>Plano Estadual de Educação</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/plano-educacao</t>
-  </si>
-  <si>
     <t>Painel de Monitoramento do PEE</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/monitoramento-pee</t>
-  </si>
-  <si>
     <t>Creches Escolares</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/creches</t>
-  </si>
-  <si>
     <t>Lista de Escolas</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/escolas</t>
-  </si>
-  <si>
     <t>Vagas para Contratação Temporária</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/vagas-temporarias</t>
-  </si>
-  <si>
     <t>Registro Público de Empresas</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/empresas</t>
-  </si>
-  <si>
     <t>Empresas Sancionadas pela Lei Anticorrupção</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/empresas-sancionadas</t>
-  </si>
-  <si>
     <t>Portal do Meio Ambiente</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/meio-ambiente</t>
-  </si>
-  <si>
     <t>EIA e RIMA</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/eia-rima</t>
-  </si>
-  <si>
     <t>Licenças Ambientais</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/licencas</t>
-  </si>
-  <si>
     <t>Painel de Contratos de Obras</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/contratos-obras</t>
-  </si>
-  <si>
     <t>Painel de Obras Públicas</t>
   </si>
   <si>
     <t>Processos de Compras – Obras</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/compras-obras</t>
-  </si>
-  <si>
     <t>Patrimônio Artístico e Cultural</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/patrimonio-cultural</t>
-  </si>
-  <si>
     <t>Plano Estadual de Saúde 2024-2027</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/plano-saude</t>
-  </si>
-  <si>
     <t>Painel do Plano Estadual de Saúde</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/painel-saude</t>
-  </si>
-  <si>
     <t>Instrumentos de Planejamento e Gestão</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/gestao-saude</t>
-  </si>
-  <si>
     <t>Vacinas</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/vacinas</t>
-  </si>
-  <si>
     <t>Lista de Medicamentos</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/medicamentos</t>
-  </si>
-  <si>
     <t>Estoque de Medicamentos</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/estoque-medicamentos</t>
-  </si>
-  <si>
     <t>Lista de Espera em Consultas e Internações</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/lista-espera</t>
-  </si>
-  <si>
     <t>Serviços Hospitalares</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/servicos-hospitalares</t>
-  </si>
-  <si>
     <t>Dados Abertos em Saúde</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/dados-saude</t>
-  </si>
-  <si>
     <t>Crimes Violentos</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/crimes-violentos</t>
-  </si>
-  <si>
     <t>Violência contra mulher</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/violencia-mulher</t>
-  </si>
-  <si>
     <t>Atendimento</t>
   </si>
   <si>
@@ -611,36 +354,21 @@
     <t>Fale Conosco – SEE</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/fale-conosco-see</t>
-  </si>
-  <si>
     <t>Fale Conosco – DETRAN MG</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/fale-conosco-detran</t>
-  </si>
-  <si>
     <t>Fale Conosco – Portal da Transparência</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/fale-conosco</t>
-  </si>
-  <si>
     <t>Lig Minas – 155</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/lig-minas</t>
-  </si>
-  <si>
     <t>Ouvidoria Geral do Estado</t>
   </si>
   <si>
     <t>Propostas e Alterações Orçamentárias</t>
   </si>
   <si>
-    <t>Portal da Transparência</t>
-  </si>
-  <si>
     <t>Planejamento e Monitoramento do PPAG</t>
   </si>
   <si>
@@ -689,9 +417,6 @@
     <t>https://www.transparencia.mg.gov.br/convenios/convenios-de-entrada/convenio-entrada</t>
   </si>
   <si>
-    <t>https://portaldatransparencia.gov.br/convenios/consulta?paginacaoSimples=true&amp;tamanhoPagina=&amp;offset=&amp;direcaoOrdenacao=asc&amp;periodoLiberacaoRecursosDe=01%2F01%2F2020&amp;periodoVigenciaDe=01%2F01%2F2020&amp;periodoVigenciaAte=30%2F09%2F2023&amp;tipoConvenente=8&amp;uf=MG&amp;colunasSelecionadas=linkDetalhamento%2CnumeroConvenio%2Cuf%2CmunicipioConvenente%2Csituacao%2CtipoTransferencia%2Cobjetivo%2CorgaoSuperior%2Corgao%2Cconcedente%2Cconvenente%2CdataInicioVigencia%2CdataFimVigencia%2CdataPublicacao%2CvalorLiberado%2</t>
-  </si>
-  <si>
     <t>https://www.casacivil.mg.gov.br/CaptacaoRecursos/Detalhe/44</t>
   </si>
   <si>
@@ -735,12 +460,279 @@
   </si>
   <si>
     <t>Transparência Temática - Segurança</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/historico-de-atualizacao</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/glossario-1</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/estrutura-do-governo-1</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/menu/proposta-e-alteracoes-orcamentarias</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/planejamento-e-resultados/proposta-alteracoes-orcamentaria/proposta-orcamentaria</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/planejamento-e-resultados/proposta-alteracoes-orcamentaria/emenda-orcamentaria</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/planejamento-e-resultados/proposta-alteracoes-orcamentaria/alteracao-orcamentaria</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/planejamento-e-resultados/proposta-alteracoes-orcamentaria/credito-orcamentario</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/planejamento-e-resultados/proposta-alteracoes-orcamentaria/obras-orcadas</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/planejamento-e-resultados/planejamento-e-monitoramento-ppag/programacao-execucao-ppag-programa/ppagprograma-programas/6/2025/0/0</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/planejamento-e-resultados/planejamento-e-monitoramento-ppag/programacao-execucao-consolidado</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/receitas/estado-receita</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/renuncias-e-desoneracoes-1</t>
+  </si>
+  <si>
+    <t>https://transparencia.mg.gov.br/despesa-estado/despesa</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/despesa-estado/restos-a-pagar</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/despesa-estado/mapa-de-investimento</t>
+  </si>
+  <si>
+    <t>https://dados.mg.gov.br/dataset/relacao_nominal_servidores</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/despesa-com-pessoal</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/terceirizados</t>
+  </si>
+  <si>
+    <t>https://www.ceape.mg.gov.br/ceape/servers</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/concursos-e-processos-seletivos/concursos-realizados</t>
+  </si>
+  <si>
+    <t>https://www.mg.gov.br/planejamento/pagina/gestao-de-pessoas/recrutamento-e-selecao/concursos-publicos</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/menu/processos-seletivos-1</t>
+  </si>
+  <si>
+    <t>https://www.fazenda.mg.gov.br/governo/contadoria_geral/lei_responsabilidade_fiscal</t>
+  </si>
+  <si>
+    <t>https://www.fazenda.mg.gov.br/governo/contadoria_geral/atendimentos_constitucionais/index_ldo_ano_atual.html</t>
+  </si>
+  <si>
+    <t>https://www.fazenda.mg.gov.br/governo/contadoria_geral/atendimentos_constitucionais</t>
+  </si>
+  <si>
+    <t>https://www.fazenda.mg.gov.br/tesouro-estadual/contadoria-geral/programa-de-reestruturacao-e-ajuste-fiscal/index.html</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/u/0/folders/1Pb_0-4u5ilYJa6Mi2tEwGKpnNlWstSDT</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/u/0/folders/1lktezuJG8pNRGAS3KjoXnlzTWVSi_1Kb</t>
+  </si>
+  <si>
+    <t>https://www.secult.mg.gov.br/documentos/lei-estadual-de-incentivo-a-cultura-leic</t>
+  </si>
+  <si>
+    <t>http://incentivo.esportes.mg.gov.br/projetos-aprovados/</t>
+  </si>
+  <si>
+    <t>https://www.bdmg.mg.gov.br/transparencia-documentos/</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/voos-do-governador</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/menu/viagens-a-servico</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/licitacoes-e-contratos/compras-e-contratos</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/notas-fiscais</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/licitacoes</t>
+  </si>
+  <si>
+    <t>https://compras.mg.gov.br/agente-publico/planejamento-de-compras-subcomp/</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/fiscais-de-contrato</t>
+  </si>
+  <si>
+    <t>https://compras.mg.gov.br/fornecedores/cadastro-de-fornecedores-impedidos-cafimp/</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/menu/transferencias-obrigatorias-1</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/acordos-de-cooperacao-tecnica</t>
+  </si>
+  <si>
+    <t>https://dados.mg.gov.br/dataset/termos-parceria-contratos-gestao</t>
+  </si>
+  <si>
+    <t>http://www.ppp.mg.gov.br/projetos/contratos-assinados/contratos-assinados</t>
+  </si>
+  <si>
+    <t>https://www.emendas.mg.gov.br/transparencia/</t>
+  </si>
+  <si>
+    <t>Execução das Emendas Parlamentares Federais</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/execucao-das-emendas-parlamentares</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/patrimonio/frota</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/patrimonio/bens-moveis</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/relatorio-de-gestao-e-balanco-geral-do-estado</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/julgamento-das-contas-do-governador-pelo-tce</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/eventos-extraordinarios/acordo-judicial/acordo-judicial-reparacao-vale</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/despesa-de-pessoal-acordo-judicial-da-vale</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/eventos-extraordinarios/covid-19/compras-contratos</t>
+  </si>
+  <si>
+    <t>https://www.dados.mg.gov.br/dataset/auxilios-financeiros</t>
+  </si>
+  <si>
+    <t>https://www.dados.mg.gov.br/dataset/programas-transferencia-renda</t>
+  </si>
+  <si>
+    <t>https://www.fazenda.mg.gov.br/empresas/Consulta-Divida-Ativa/Relatorios</t>
+  </si>
+  <si>
+    <t>https://www.fazenda.mg.gov.br/tesouro-estadual/divida-publica/portal-da-divida-publica-estadual</t>
+  </si>
+  <si>
+    <t>https://www.educacao.mg.gov.br/plano-estadual-de-educacao/</t>
+  </si>
+  <si>
+    <t>https://lookerstudio.google.com/u/0/reporting/ec9c0100-72ec-4048-b94c-6fd37374aff1/page/p_u2uzahpktc</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/creches-escolares</t>
+  </si>
+  <si>
+    <t>https://www.educacao.mg.gov.br/escolas/painel-escolas-de-minas/</t>
+  </si>
+  <si>
+    <t>https://controlequadropessoal.educacao.mg.gov.br/divulgacao</t>
+  </si>
+  <si>
+    <t>https://jucemg.mg.gov.br/estatisticas</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/empresas-sancionadas-pela-lei-anticorrupcao-1</t>
+  </si>
+  <si>
+    <t>https://transparencia.meioambiente.mg.gov.br/</t>
+  </si>
+  <si>
+    <t>https://feam.br/web/feam/elabora%C3%A7%C3%A3o-de-estudo-de-impacto/relat%C3%B3rio-de-impacto-ambiental-eia/rima-</t>
+  </si>
+  <si>
+    <t>https://ecosistemas.meioambiente.mg.gov.br/sla/#/acesso-visitante</t>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/view?r=eyJrIjoiMzkwZGM3MGItZGUyNS00NGMzLThkY2YtNTNhYzk0OGYwMzM5IiwidCI6IjUyZTU3MzMxLWYyNzgtNGNhMC05NmZkLTk0YzVhYjFmODUyNCJ9&amp;disablecdnExpiration=1747778049</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/obras-publicas</t>
+  </si>
+  <si>
+    <t>https://www1.compras.mg.gov.br/obra/consulta/consultaObra.html?_gl=1*10rhe7s*_ga*MTc5MDMwMjQ3Ni4xNzQwNDAwNjM0*_ga_K12Q555D01*MTc0MDU4ODcwNi41LjEuMTc0MDU5MTQ2MC4wLjAuMA..</t>
+  </si>
+  <si>
+    <t>https://www.dados.mg.gov.br/organization/instituto-estadual-do-patrimonio-historico-e-artistico-de-minas-gerais-iepha</t>
+  </si>
+  <si>
+    <t>https://www.saude.mg.gov.br/wp-content/uploads/2021/01/PES-24-27-04.2024-1-217.pdf</t>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/view?r=eyJrIjoiZGYyMGNmZWUtMWNjNy00YjdjLWEwZjgtZTg4M2VkOGI5MWM1IiwidCI6Ijg3ZTRkYTJiLTgyZGYtNDhmNi05MTU3LTY5YzNjYTYwMGRmMiIsImMiOjR9</t>
+  </si>
+  <si>
+    <t>https://www.saude.mg.gov.br/instrumentos-de-planejamento-e-gestao-do-sus/</t>
+  </si>
+  <si>
+    <t>https://www.saude.mg.gov.br/vacinamaisminas/</t>
+  </si>
+  <si>
+    <t>https://www.saude.mg.gov.br/obtermedicamentos/</t>
+  </si>
+  <si>
+    <t>https://www.saude.mg.gov.br/obtermedicamentos/ceaf/estoque-ceaf/</t>
+  </si>
+  <si>
+    <t>https://info.saude.mg.gov.br/8/paineis/32</t>
+  </si>
+  <si>
+    <t>https://www.fhemig.mg.gov.br/atendimento/horarios-de-atendimento-dos-hospitais-da-rede-fhemig</t>
+  </si>
+  <si>
+    <t>https://www.dados.mg.gov.br/group/saude</t>
+  </si>
+  <si>
+    <t>https://www.dados.mg.gov.br/dataset/crimes-violentos</t>
+  </si>
+  <si>
+    <t>https://www.dados.mg.gov.br/dataset/violencia-contra-mulher</t>
+  </si>
+  <si>
+    <t>https://acessoainformacao.mg.gov.br/sistema/site/index.aspx</t>
+  </si>
+  <si>
+    <t>https://faleconosco.mg.gov.br/ligminas-bpms-frontend/publico/br/gov/prodemge/seplag/ligminasbpms/visao/processos/RegistrarAtendimentoFaleConosco.zul?processo=PROC_00093&amp;atividade=ATIV_00388&amp;site=SEE</t>
+  </si>
+  <si>
+    <t>https://detran.mg.gov.br/atendimento</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/fale-conosco-portal-da-transparencia</t>
+  </si>
+  <si>
+    <t>https://www.mg.gov.br/pagina/ligminas-155</t>
+  </si>
+  <si>
+    <t>https://www.ouvidoriageral.mg.gov.br/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1079,12 +1071,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="63.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
     <col min="3" max="3" width="95.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1115,10 +1107,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1126,10 +1118,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1140,7 +1132,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1148,1082 +1140,1082 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>203</v>
+        <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>42</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>46</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>206</v>
+        <v>115</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>206</v>
+        <v>115</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>206</v>
+        <v>115</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>63</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>65</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>207</v>
+        <v>116</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>74</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>207</v>
+        <v>116</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>207</v>
+        <v>116</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>78</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>207</v>
+        <v>116</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>207</v>
+        <v>116</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>82</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>207</v>
+        <v>116</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>84</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>207</v>
+        <v>116</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>89</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>101</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>20</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>103</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>105</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>209</v>
+        <v>118</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>209</v>
+        <v>118</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>210</v>
+        <v>119</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>212</v>
+        <v>121</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>213</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>210</v>
+        <v>119</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>214</v>
+        <v>123</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>215</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>211</v>
+        <v>120</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>217</v>
+        <v>126</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>211</v>
+        <v>120</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>211</v>
+        <v>120</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>222</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>216</v>
+        <v>125</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>112</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>216</v>
+        <v>125</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>216</v>
+        <v>125</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>119</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>121</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>223</v>
+        <v>131</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>223</v>
+        <v>131</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>133</v>
+        <v>197</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>139</v>
+        <v>200</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>141</v>
+        <v>201</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>229</v>
+        <v>137</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>228</v>
+        <v>136</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>144</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>148</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>149</v>
+        <v>84</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>231</v>
+        <v>139</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>231</v>
+        <v>139</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>155</v>
+        <v>87</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>156</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>232</v>
+        <v>140</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>158</v>
+        <v>210</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>232</v>
+        <v>140</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>232</v>
+        <v>140</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>162</v>
+        <v>212</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>233</v>
+        <v>141</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>164</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>233</v>
+        <v>141</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>165</v>
+        <v>92</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>22</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>233</v>
+        <v>141</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>167</v>
+        <v>215</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>234</v>
+        <v>142</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>168</v>
+        <v>94</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>171</v>
+        <v>217</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>172</v>
+        <v>96</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>176</v>
+        <v>98</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>178</v>
+        <v>99</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>182</v>
+        <v>101</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>236</v>
+        <v>144</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>236</v>
+        <v>144</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>27</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>198</v>
+        <v>110</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>26</v>
+        <v>233</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>

--- a/upload/mapadosite.xlsx
+++ b/upload/mapadosite.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678A4233-E537-4BC7-A922-0C625B194E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17370" windowHeight="6420"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="232">
   <si>
     <t>Categoria</t>
   </si>
@@ -90,9 +89,6 @@
     <t>Leis Orçamentárias</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/leis-orcamentarias</t>
-  </si>
-  <si>
     <t>Proposta Orçamentária</t>
   </si>
   <si>
@@ -135,9 +131,6 @@
     <t>Terceirizados</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/terceirizados</t>
-  </si>
-  <si>
     <t>Relação Nominal dos Servidores</t>
   </si>
   <si>
@@ -366,9 +359,6 @@
     <t>Ouvidoria Geral do Estado</t>
   </si>
   <si>
-    <t>Propostas e Alterações Orçamentárias</t>
-  </si>
-  <si>
     <t>Planejamento e Monitoramento do PPAG</t>
   </si>
   <si>
@@ -471,9 +461,6 @@
     <t>https://www.transparencia.mg.gov.br/pagina/estrutura-do-governo-1</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/menu/proposta-e-alteracoes-orcamentarias</t>
-  </si>
-  <si>
     <t>https://www.transparencia.mg.gov.br/planejamento-e-resultados/proposta-alteracoes-orcamentaria/proposta-orcamentaria</t>
   </si>
   <si>
@@ -561,9 +548,6 @@
     <t>https://www.transparencia.mg.gov.br/pagina/voos-do-governador</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/menu/viagens-a-servico</t>
-  </si>
-  <si>
     <t>https://www.transparencia.mg.gov.br/licitacoes-e-contratos/compras-e-contratos</t>
   </si>
   <si>
@@ -702,9 +686,6 @@
     <t>https://www.fhemig.mg.gov.br/atendimento/horarios-de-atendimento-dos-hospitais-da-rede-fhemig</t>
   </si>
   <si>
-    <t>https://www.dados.mg.gov.br/group/saude</t>
-  </si>
-  <si>
     <t>https://www.dados.mg.gov.br/dataset/crimes-violentos</t>
   </si>
   <si>
@@ -727,12 +708,24 @@
   </si>
   <si>
     <t>https://www.ouvidoriageral.mg.gov.br/</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/leis-orcamentarias</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/estagiarios</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/diarias-e-viagens/viagens</t>
+  </si>
+  <si>
+    <t>https://www.dados.mg.gov.br/organization/secretaria-de-estado-de-saude-ses</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1071,8 +1064,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C103"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.7109375" bestFit="1" customWidth="1"/>
@@ -1110,7 +1103,7 @@
         <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1132,7 +1125,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1143,7 +1136,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1154,18 +1147,18 @@
         <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1176,10 +1169,10 @@
         <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1187,10 +1180,10 @@
         <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
@@ -1198,10 +1191,10 @@
         <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -1209,40 +1202,40 @@
         <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1250,54 +1243,54 @@
         <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>160</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1308,7 +1301,7 @@
         <v>32</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1319,7 +1312,7 @@
         <v>33</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1330,7 +1323,7 @@
         <v>34</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1341,7 +1334,7 @@
         <v>35</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1349,384 +1342,384 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C30" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="C34" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>176</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="C40" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C47" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>130</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="C59" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1734,109 +1727,109 @@
         <v>16</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B63" s="2" t="s">
+      <c r="C63" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="C64" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B67" s="2" t="s">
+      <c r="C67" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="C68" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1844,378 +1837,367 @@
         <v>134</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>202</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="C71" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="B72" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C75" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C75" s="2" t="s">
+    <row r="79" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>206</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="C81" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B83" s="2" t="s">
+      <c r="C83" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="C84" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B87" s="2" t="s">
+      <c r="C87" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="C88" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B91" s="2" t="s">
+      <c r="C91" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="C92" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="C97" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B99" s="2" t="s">
+      <c r="C99" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="C100" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C103" s="2" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>

--- a/upload/mapadosite.xlsx
+++ b/upload/mapadosite.xlsx
@@ -5,15 +5,18 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m13368964\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17370" windowHeight="6420"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8490"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$105</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -24,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="233">
   <si>
     <t>Categoria</t>
   </si>
@@ -137,9 +140,6 @@
     <t>Cadastro CEAPE</t>
   </si>
   <si>
-    <t>Concursos</t>
-  </si>
-  <si>
     <t>Concursos realizados</t>
   </si>
   <si>
@@ -149,42 +149,6 @@
     <t>Processos seletivos</t>
   </si>
   <si>
-    <t>Relatório de Gestão Fiscal – RGF</t>
-  </si>
-  <si>
-    <t>Relatório Resumido da Execução Orçamentária – RREO</t>
-  </si>
-  <si>
-    <t>Demonstrativos Quadrimestrais</t>
-  </si>
-  <si>
-    <t>Índices Constitucionais</t>
-  </si>
-  <si>
-    <t>Programas de Reestruturação e Ajuste</t>
-  </si>
-  <si>
-    <t>Fundo de Erradicação da Miséria</t>
-  </si>
-  <si>
-    <t>Programas Sociais</t>
-  </si>
-  <si>
-    <t>Incentivos</t>
-  </si>
-  <si>
-    <t>Incentivos Culturais</t>
-  </si>
-  <si>
-    <t>Incentivos Esportivos</t>
-  </si>
-  <si>
-    <t>Crédito e Financiamento do Setor Público</t>
-  </si>
-  <si>
-    <t>Viagens</t>
-  </si>
-  <si>
     <t>Diárias e Viagens</t>
   </si>
   <si>
@@ -212,9 +176,6 @@
     <t>Transferências recebidas do Governo Federal</t>
   </si>
   <si>
-    <t>Termos de Parcerias</t>
-  </si>
-  <si>
     <t>Acordos de Cooperação Técnica</t>
   </si>
   <si>
@@ -233,18 +194,12 @@
     <t>Bens Móveis</t>
   </si>
   <si>
-    <t>Contas do Governador</t>
-  </si>
-  <si>
     <t>Relatório de Gestão e Balanço Geral do Estado</t>
   </si>
   <si>
     <t>Julgamento das Contas pelo TCE</t>
   </si>
   <si>
-    <t>Acordo Judicial de Reparação da Vale</t>
-  </si>
-  <si>
     <t>Despesa de Pessoal – Acordo Vale</t>
   </si>
   <si>
@@ -266,9 +221,6 @@
     <t>Plano Estadual de Educação</t>
   </si>
   <si>
-    <t>Painel de Monitoramento do PEE</t>
-  </si>
-  <si>
     <t>Creches Escolares</t>
   </si>
   <si>
@@ -293,15 +245,6 @@
     <t>Licenças Ambientais</t>
   </si>
   <si>
-    <t>Painel de Contratos de Obras</t>
-  </si>
-  <si>
-    <t>Painel de Obras Públicas</t>
-  </si>
-  <si>
-    <t>Processos de Compras – Obras</t>
-  </si>
-  <si>
     <t>Patrimônio Artístico e Cultural</t>
   </si>
   <si>
@@ -365,93 +308,30 @@
     <t>Despesas Públicas</t>
   </si>
   <si>
-    <t>Relatórios da Lei de Responsabilidade Fiscal – LRF</t>
-  </si>
-  <si>
     <t>Licitações e Contratos</t>
   </si>
   <si>
     <t>Transferências Obrigatórias</t>
   </si>
   <si>
-    <t>Convênios de Saída</t>
-  </si>
-  <si>
-    <t>Convênios de Entrada</t>
-  </si>
-  <si>
     <t>Convênios / Parcerias de Saída de Recursos</t>
   </si>
   <si>
     <t>https://www.transparencia.mg.gov.br/convenios/convenios-de-saida-de-recursos/convenios-de-saida</t>
   </si>
   <si>
-    <t>Convênios de Saída e Parceria MROSC  </t>
-  </si>
-  <si>
-    <t>https://app.powerbi.com/view?r=eyJrIjoiMzY1NjVkNzgtZDlhYy00ZWI0LThhM2UtMjY5MzliMzkzYWU2IiwidCI6ImU1ZDNhZTdjLTliMzgtNDhkZS1hMDg3LWY2NzM0YTI4NzU3NCJ9</t>
-  </si>
-  <si>
     <t>Convênios e Parcerias</t>
   </si>
   <si>
     <t>Convênios de Entrada de Recursos</t>
   </si>
   <si>
-    <t>Convênios de Entrada – Portal Federal</t>
-  </si>
-  <si>
-    <t>Painel de Monitoramenteo dos Instrumentos de Entrada de Recursos</t>
-  </si>
-  <si>
-    <t>https://www.transparencia.mg.gov.br/convenios/convenios-de-entrada/convenio-entrada</t>
-  </si>
-  <si>
-    <t>https://www.casacivil.mg.gov.br/CaptacaoRecursos/Detalhe/44</t>
-  </si>
-  <si>
-    <t>Transparência Temática - Acordos</t>
-  </si>
-  <si>
-    <t>Transparência Temática - COVID</t>
-  </si>
-  <si>
-    <t>Transparência Temática - Desenvolvimento Social</t>
-  </si>
-  <si>
-    <t>Transparência Temática - Dívidas</t>
-  </si>
-  <si>
     <t>https://dataviva.info/</t>
   </si>
   <si>
     <t>Economia</t>
   </si>
   <si>
-    <t>Transparência Temática - Economia</t>
-  </si>
-  <si>
-    <t>Transparência Temática - Educação</t>
-  </si>
-  <si>
-    <t>Transparência Temática - Empresas</t>
-  </si>
-  <si>
-    <t>Transparência Temática - Meio Ambiente</t>
-  </si>
-  <si>
-    <t>Transparência Temática - Obras</t>
-  </si>
-  <si>
-    <t>Transparência Temática - Patrimônio Artístico e Cultural</t>
-  </si>
-  <si>
-    <t>Transparência Temática - Saúde</t>
-  </si>
-  <si>
-    <t>Transparência Temática - Segurança</t>
-  </si>
-  <si>
     <t>https://www.transparencia.mg.gov.br/pagina/historico-de-atualizacao</t>
   </si>
   <si>
@@ -623,9 +503,6 @@
     <t>https://www.educacao.mg.gov.br/plano-estadual-de-educacao/</t>
   </si>
   <si>
-    <t>https://lookerstudio.google.com/u/0/reporting/ec9c0100-72ec-4048-b94c-6fd37374aff1/page/p_u2uzahpktc</t>
-  </si>
-  <si>
     <t>https://www.transparencia.mg.gov.br/pagina/creches-escolares</t>
   </si>
   <si>
@@ -650,15 +527,9 @@
     <t>https://ecosistemas.meioambiente.mg.gov.br/sla/#/acesso-visitante</t>
   </si>
   <si>
-    <t>https://app.powerbi.com/view?r=eyJrIjoiMzkwZGM3MGItZGUyNS00NGMzLThkY2YtNTNhYzk0OGYwMzM5IiwidCI6IjUyZTU3MzMxLWYyNzgtNGNhMC05NmZkLTk0YzVhYjFmODUyNCJ9&amp;disablecdnExpiration=1747778049</t>
-  </si>
-  <si>
     <t>https://www.transparencia.mg.gov.br/pagina/obras-publicas</t>
   </si>
   <si>
-    <t>https://www1.compras.mg.gov.br/obra/consulta/consultaObra.html?_gl=1*10rhe7s*_ga*MTc5MDMwMjQ3Ni4xNzQwNDAwNjM0*_ga_K12Q555D01*MTc0MDU4ODcwNi41LjEuMTc0MDU5MTQ2MC4wLjAuMA..</t>
-  </si>
-  <si>
     <t>https://www.dados.mg.gov.br/organization/instituto-estadual-do-patrimonio-historico-e-artistico-de-minas-gerais-iepha</t>
   </si>
   <si>
@@ -720,6 +591,141 @@
   </si>
   <si>
     <t>https://www.dados.mg.gov.br/organization/secretaria-de-estado-de-saude-ses</t>
+  </si>
+  <si>
+    <t>Beneficiários das Desonerações Tributárias</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/beneficiarios-das-desoneracoes-tributarias</t>
+  </si>
+  <si>
+    <t>Despesa por  empenho</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/despesa-por-empenho</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/ordem-cronologica</t>
+  </si>
+  <si>
+    <t>Ordem Cronológica</t>
+  </si>
+  <si>
+    <t>Legislação das Carreiras</t>
+  </si>
+  <si>
+    <t>Tabelas de Vencimento Básico</t>
+  </si>
+  <si>
+    <t>https://www.mg.gov.br/planejamento/pagina/gestao-de-pessoas/legislacao/legislacao-de-carreira</t>
+  </si>
+  <si>
+    <t>https://www.mg.gov.br/planejamento/pagina/gestao-de-pessoas/carreiras-e-remuneracao/tabelas-de-vencimento-basico</t>
+  </si>
+  <si>
+    <t>Concursos e Processos Seletivos</t>
+  </si>
+  <si>
+    <t>Gestão Fiscal e Governamental</t>
+  </si>
+  <si>
+    <t>Relatórios da Lei de Responsabilidade Fiscal / Relatório de Gestão Fiscal – RGF</t>
+  </si>
+  <si>
+    <t>Relatórios da Lei de Responsabilidade Fiscal / Relatório Resumido da Execução Orçamentária – RREO</t>
+  </si>
+  <si>
+    <t>Relatórios da Lei de Responsabilidade Fiscal /Demonstrativos Quadrimestrais</t>
+  </si>
+  <si>
+    <t>Relatórios da Lei de Responsabilidade Fiscal/ Atendimento aos Índices Constitucionais</t>
+  </si>
+  <si>
+    <t>Relatórios da Lei de Responsabilidade Fiscal / Programas de Reestruturação e Ajuste Fiscal</t>
+  </si>
+  <si>
+    <t>Relatórios da Lei de Responsabilidade Fiscal / Fundo de Erradicação da Miséria</t>
+  </si>
+  <si>
+    <t>Relatórios da Lei de Responsabilidade Fiscal / Programas Sociais</t>
+  </si>
+  <si>
+    <t>Incentivos / Crédito e Financiamento do Setor Público</t>
+  </si>
+  <si>
+    <t>Incentivos / Incentivos Esportivos</t>
+  </si>
+  <si>
+    <t>Incentivos / Incentivos Culturais</t>
+  </si>
+  <si>
+    <t>Contas Anuais do Governador</t>
+  </si>
+  <si>
+    <t>Viagens a Serviço</t>
+  </si>
+  <si>
+    <t>Tabela de Diárias e Viagens</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/legislacao-mineira/DEC/47045/2016</t>
+  </si>
+  <si>
+    <t>Contratos</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/contratos</t>
+  </si>
+  <si>
+    <t>Termos de Parcerias e Contratos de Gestão</t>
+  </si>
+  <si>
+    <t>Acordos Judiciais de Reparação</t>
+  </si>
+  <si>
+    <t>Execução do Acordo Judicial de Reparação da Vale</t>
+  </si>
+  <si>
+    <t>Acordo Judicial de Reparação do Rio Doce</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/acordo-judicial-de-reparacao-do-rio-doce</t>
+  </si>
+  <si>
+    <t>COVID</t>
+  </si>
+  <si>
+    <t>Desenvolvimento Social</t>
+  </si>
+  <si>
+    <t>Educação</t>
+  </si>
+  <si>
+    <t>FUNDEB</t>
+  </si>
+  <si>
+    <t>https://fundeb.educacao.mg.gov.br/index.php/documentos/atas</t>
+  </si>
+  <si>
+    <t>Empresas</t>
+  </si>
+  <si>
+    <t>Meio Ambiente</t>
+  </si>
+  <si>
+    <t>Obras Públicas</t>
+  </si>
+  <si>
+    <t>Saúde</t>
+  </si>
+  <si>
+    <t>Segurança</t>
+  </si>
+  <si>
+    <t>Dívidas</t>
+  </si>
+  <si>
+    <t>Atualização de links</t>
   </si>
 </sst>
 </file>
@@ -772,7 +778,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -784,6 +790,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1065,11 +1077,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
     <col min="3" max="3" width="95.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1103,14 +1115,14 @@
         <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -1121,220 +1133,220 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>143</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>97</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>22</v>
+      <c r="B9" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>23</v>
+        <v>222</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>11</v>
+        <v>93</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>198</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>154</v>
+        <v>93</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>155</v>
+        <v>97</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>156</v>
+        <v>97</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>221</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>13</v>
+        <v>223</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>229</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>229</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1342,864 +1354,912 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>217</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>162</v>
+        <v>190</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>113</v>
+        <v>211</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>113</v>
+        <v>231</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>113</v>
+        <v>198</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>113</v>
+        <v>227</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>113</v>
+        <v>226</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>48</v>
+        <v>229</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>52</v>
+        <v>217</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>53</v>
+        <v>218</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>230</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>114</v>
+        <v>223</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>175</v>
+        <v>224</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>114</v>
+        <v>231</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>57</v>
+        <v>207</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>178</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>115</v>
+        <v>229</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>115</v>
+        <v>210</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>116</v>
+        <v>13</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>117</v>
+        <v>227</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>122</v>
+        <v>229</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>122</v>
+        <v>229</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>183</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>184</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>185</v>
+        <v>25</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>186</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>16</v>
+        <v>228</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>187</v>
+        <v>228</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>69</v>
+        <v>229</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="B64" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>130</v>
+        <v>229</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>135</v>
+        <v>222</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>135</v>
+        <v>11</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>135</v>
+        <v>226</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>203</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="C79" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="C80" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>138</v>
+        <v>199</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>89</v>
+        <v>200</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>138</v>
+        <v>199</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>90</v>
+        <v>201</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>209</v>
+        <v>123</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>138</v>
+        <v>199</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>91</v>
+        <v>202</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="B87" s="2" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>214</v>
+        <v>114</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>140</v>
+        <v>229</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>140</v>
+        <v>211</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>218</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>100</v>
+        <v>216</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>219</v>
+        <v>141</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>220</v>
+        <v>139</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>141</v>
+        <v>229</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>104</v>
+        <v>223</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>104</v>
+        <v>230</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>104</v>
+        <v>211</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>226</v>
+        <v>179</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>227</v>
+        <v>180</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C105" s="2" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C105">
+    <sortState ref="A7:E98">
+      <sortCondition ref="B1:B105"/>
+    </sortState>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C11" r:id="rId2"/>
+    <hyperlink ref="C27" r:id="rId3"/>
+    <hyperlink ref="C60" r:id="rId4"/>
+    <hyperlink ref="C49" r:id="rId5"/>
+    <hyperlink ref="C90" r:id="rId6"/>
+    <hyperlink ref="C89" r:id="rId7"/>
+    <hyperlink ref="C17" r:id="rId8"/>
+    <hyperlink ref="C7" r:id="rId9"/>
+    <hyperlink ref="C42" r:id="rId10"/>
+    <hyperlink ref="C59" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>
--- a/upload/mapadosite.xlsx
+++ b/upload/mapadosite.xlsx
@@ -263,9 +263,6 @@
     <t>Crimes Violentos</t>
   </si>
   <si>
-    <t>Violência contra mulher</t>
-  </si>
-  <si>
     <t>Atendimento</t>
   </si>
   <si>
@@ -749,7 +746,10 @@
     <t>Demonstrativos Quadrimestrais</t>
   </si>
   <si>
-    <t xml:space="preserve"> Atendimento aos Índices Constitucionais</t>
+    <t>Violência Contra Mulher</t>
+  </si>
+  <si>
+    <t>Atendimento aos Índices Constitucionais</t>
   </si>
 </sst>
 </file>
@@ -1112,7 +1112,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -1149,12 +1149,12 @@
         <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -1168,7 +1168,7 @@
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -1177,12 +1177,12 @@
         <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
@@ -1191,110 +1191,110 @@
         <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>93</v>
-      </c>
       <c r="D9" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>44</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>54</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1303,12 +1303,12 @@
         <v>49</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>13</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>13</v>
@@ -1331,12 +1331,12 @@
         <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>13</v>
@@ -1345,12 +1345,12 @@
         <v>31</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>13</v>
@@ -1359,12 +1359,12 @@
         <v>32</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>13</v>
@@ -1373,348 +1373,348 @@
         <v>33</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -1723,124 +1723,124 @@
         <v>48</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="D47" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>19</v>
@@ -1849,138 +1849,138 @@
         <v>20</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>46</v>
@@ -1989,40 +1989,40 @@
         <v>47</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>67</v>
@@ -2031,533 +2031,533 @@
         <v>67</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>41</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="D80" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>240</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="D89" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="D98" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>9</v>
@@ -2568,44 +2568,44 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/upload/mapadosite.xlsx
+++ b/upload/mapadosite.xlsx
@@ -1106,7 +1106,7 @@
   <cols>
     <col min="1" max="1" width="32.42578125" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="91.140625" customWidth="1"/>
+    <col min="3" max="3" width="68.5703125" customWidth="1"/>
     <col min="4" max="4" width="95.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1269,13 +1269,13 @@
         <v>216</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>54</v>
+        <v>199</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1437,13 +1437,13 @@
         <v>216</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>53</v>
+        <v>199</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1451,13 +1451,13 @@
         <v>216</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>59</v>
+        <v>203</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1479,13 +1479,13 @@
         <v>216</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>77</v>
+        <v>204</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1493,13 +1493,13 @@
         <v>216</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1507,13 +1507,13 @@
         <v>216</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1566,10 +1566,10 @@
         <v>213</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1605,13 +1605,13 @@
         <v>216</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1629,17 +1629,17 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>155</v>
+        <v>206</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1647,13 +1647,13 @@
         <v>216</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1675,13 +1675,13 @@
         <v>216</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1734,24 +1734,24 @@
         <v>205</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>207</v>
+        <v>61</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="A46" t="s">
         <v>216</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1801,13 +1801,13 @@
         <v>216</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1860,10 +1860,10 @@
         <v>209</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1871,13 +1871,13 @@
         <v>216</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1885,13 +1885,13 @@
         <v>216</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1899,13 +1899,13 @@
         <v>216</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>165</v>
+        <v>210</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1955,13 +1955,13 @@
         <v>216</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>210</v>
+        <v>67</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>159</v>
+        <v>67</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2000,10 +2000,10 @@
         <v>211</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2025,13 +2025,13 @@
         <v>216</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>67</v>
+        <v>211</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2067,13 +2067,13 @@
         <v>216</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2084,10 +2084,10 @@
         <v>211</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2095,13 +2095,13 @@
         <v>216</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2151,13 +2151,13 @@
         <v>216</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2193,13 +2193,13 @@
         <v>216</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2431,13 +2431,13 @@
         <v>216</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2609,7 +2609,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D107"/>
+  <autoFilter ref="A1:D107">
+    <sortState ref="A7:D96">
+      <sortCondition ref="B1:B107"/>
+    </sortState>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1"/>
     <hyperlink ref="D13" r:id="rId2"/>
@@ -2620,8 +2624,8 @@
     <hyperlink ref="D89" r:id="rId7"/>
     <hyperlink ref="D23" r:id="rId8"/>
     <hyperlink ref="D7" r:id="rId9"/>
-    <hyperlink ref="D45" r:id="rId10"/>
-    <hyperlink ref="D61" r:id="rId11"/>
+    <hyperlink ref="D38" r:id="rId10"/>
+    <hyperlink ref="D57" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>

--- a/upload/mapadosite.xlsx
+++ b/upload/mapadosite.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="243">
   <si>
     <t>Categoria</t>
   </si>
@@ -725,9 +725,6 @@
     <t>Incentivos Esportivos</t>
   </si>
   <si>
-    <t>Relatórios da Lei de Responsabilidade Fiscal</t>
-  </si>
-  <si>
     <t>Fundo de Erradicação da Miséria</t>
   </si>
   <si>
@@ -750,6 +747,15 @@
   </si>
   <si>
     <t>Atendimento aos Índices Constitucionais</t>
+  </si>
+  <si>
+    <t>Relatórios da Lei de Responsabilidade Fiscal - LRF</t>
+  </si>
+  <si>
+    <t>Atas de Registro de Preços</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/ata-de-registro-de-precos</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" customWidth="1"/>
@@ -2221,10 +2227,10 @@
         <v>217</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>120</v>
@@ -2235,10 +2241,10 @@
         <v>217</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>119</v>
@@ -2249,10 +2255,10 @@
         <v>217</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>121</v>
@@ -2263,10 +2269,10 @@
         <v>217</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>116</v>
@@ -2277,10 +2283,10 @@
         <v>217</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>116</v>
@@ -2291,10 +2297,10 @@
         <v>217</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>117</v>
@@ -2305,10 +2311,10 @@
         <v>217</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>118</v>
@@ -2448,7 +2454,7 @@
         <v>212</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>170</v>
@@ -2606,6 +2612,20 @@
       </c>
       <c r="D107" s="2" t="s">
         <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -2626,8 +2646,9 @@
     <hyperlink ref="D7" r:id="rId9"/>
     <hyperlink ref="D38" r:id="rId10"/>
     <hyperlink ref="D57" r:id="rId11"/>
+    <hyperlink ref="D108" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>